--- a/electrician_forms/020_electrical_panel_inspection_checklist--electrician_forms.xlsx
+++ b/electrician_forms/020_electrical_panel_inspection_checklist--electrician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-phase'}</t>
+          <t>1-phase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-Phase'}</t>
+          <t>1-Phase</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-phase'}</t>
+          <t>3-phase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-Phase'}</t>
+          <t>3-Phase</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'4-phase'}</t>
+          <t>4-phase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '4-Phase'}</t>
+          <t>4-Phase</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'nema'}</t>
+          <t>nema</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'NEMA'}</t>
+          <t>NEMA</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'iec'}</t>
+          <t>iec</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'IEC'}</t>
+          <t>IEC</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ul'}</t>
+          <t>ul</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'UL'}</t>
+          <t>UL</t>
         </is>
       </c>
     </row>
